--- a/results/H-urban5.xlsx
+++ b/results/H-urban5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alessiosclafani/Desktop/PhD/crawford/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36E341C9-C16C-724F-A35E-4837677B99D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CE90227-719D-3045-A9CA-E2A066970899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="580" yWindow="760" windowWidth="28040" windowHeight="17060" activeTab="2" xr2:uid="{339F1D85-E761-C846-B29A-0F321A4073E3}"/>
   </bookViews>
@@ -17,6 +17,9 @@
     <sheet name="H-napoli5" sheetId="2" r:id="rId2"/>
     <sheet name="H-milano5" sheetId="1" r:id="rId3"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId4"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -38,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="169">
   <si>
     <t>True</t>
   </si>
@@ -542,13 +545,23 @@
   </si>
   <si>
     <t>MILANO-50-5-nc</t>
+  </si>
+  <si>
+    <t>GAP-MM</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -574,14 +587,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
+    <cellStyle name="Percentuale" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -594,6 +610,779 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="MM-roma5"/>
+      <sheetName val="MM-napoli5"/>
+      <sheetName val="MM-milano5"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="S2">
+            <v>14.0116393378949</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="S3">
+            <v>13.2519321021894</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="S4">
+            <v>9.4684939676164692</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="S5">
+            <v>8.4207899670721407</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="S6">
+            <v>13.021038220526499</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="S7">
+            <v>13.0018244171813</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="S8">
+            <v>10.948531278160701</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="S9">
+            <v>7.0885352245955202</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="S10">
+            <v>6.5929822595916203</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="S11">
+            <v>9.7350650267323005</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="S12">
+            <v>18.384401701466999</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="S13">
+            <v>18.420736431439899</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="S14">
+            <v>32.120677785006897</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="S15">
+            <v>18.618623334082798</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="S16">
+            <v>25.869340638354199</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="S17">
+            <v>25.3895790155564</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="S18">
+            <v>20.220438934522399</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="S19">
+            <v>29.149228041303001</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="S20">
+            <v>24.136609094884399</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="S21">
+            <v>23.385736204396999</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="S22">
+            <v>34.0050005331249</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="S23">
+            <v>43.338289367497701</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="S24">
+            <v>25.536833953888902</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="S25">
+            <v>35.741945260230501</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="S26">
+            <v>36.420871516475799</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="S27">
+            <v>35.0345546692919</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="S28">
+            <v>37.114686834597698</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="S29">
+            <v>35.652133408131697</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="S30">
+            <v>38.346424301624097</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="S31">
+            <v>34.178202019030302</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="S32">
+            <v>55.166126688926198</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="S33">
+            <v>48.316938586479402</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="S34">
+            <v>40.962540561998303</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="S35">
+            <v>42.870411943813899</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="S36">
+            <v>38.195181091642397</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="S37">
+            <v>46.334736795900099</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="S38">
+            <v>46.917507657479597</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="S39">
+            <v>35.845019127102901</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="S40">
+            <v>46.003883159006598</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="S41">
+            <v>49.967937097539298</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="S42">
+            <v>60.453513568892099</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="S43">
+            <v>67.694211186069495</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="S44">
+            <v>64.258363530394504</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="S45">
+            <v>59.804840922733199</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="S46">
+            <v>63.397345756324</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="S47">
+            <v>63.033771797798998</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="S48">
+            <v>64.180183753846407</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="S49">
+            <v>59.510565189664099</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="S50">
+            <v>60.385712594362303</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="S51">
+            <v>66.066139663268999</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="S2">
+            <v>14.3490194132602</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="S3">
+            <v>8.1845214300659599</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="S4">
+            <v>6.3762983166081399</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="S5">
+            <v>6.1228968146935996</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="S6">
+            <v>11.8335770772805</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="S7">
+            <v>11.5563138364442</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="S8">
+            <v>13.3100256070644</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="S9">
+            <v>10.3845350143391</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="S10">
+            <v>8.1944445910219308</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="S11">
+            <v>9.3128370665481004</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="S12">
+            <v>17.7255576921653</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="S13">
+            <v>23.223030025505299</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="S14">
+            <v>21.883621559940298</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="S15">
+            <v>23.43533925393</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="S16">
+            <v>22.3571867937866</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="S17">
+            <v>19.243079210271201</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="S18">
+            <v>21.419621230922999</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="S19">
+            <v>22.162198908187801</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="S20">
+            <v>20.979596911132901</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="S21">
+            <v>22.218812096368801</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="S22">
+            <v>24.170958900429302</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="S23">
+            <v>28.174115038064599</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="S24">
+            <v>28.785920280754102</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="S25">
+            <v>42.354737273464401</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="S26">
+            <v>30.668838719957101</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="S27">
+            <v>21.7491655134518</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="S28">
+            <v>30.043915146355499</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="S29">
+            <v>39.1659886233858</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="S30">
+            <v>36.072375318939301</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="S31">
+            <v>29.3249322828351</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="S32">
+            <v>33.4651381074003</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="S33">
+            <v>45.726008790425603</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="S34">
+            <v>34.744323996596101</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="S35">
+            <v>42.393048266850798</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="S36">
+            <v>37.310520820975597</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="S37">
+            <v>34.648496910041999</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="S38">
+            <v>39.012260954671298</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="S39">
+            <v>29.787682163917101</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="S40">
+            <v>38.3377909130257</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="S41">
+            <v>42.140421313407401</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="S42">
+            <v>40.9176513691704</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="S43">
+            <v>43.5856472760941</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="S44">
+            <v>54.704813686601902</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="S45">
+            <v>51.555063488425802</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="S46">
+            <v>61.221461321562401</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="S47">
+            <v>48.7368849048732</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="S48">
+            <v>45.675368236826102</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="S49">
+            <v>51.655480989081703</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="S50">
+            <v>49.3757628872429</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="S51">
+            <v>49.670916540677503</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2">
+        <row r="2">
+          <cell r="S2">
+            <v>12.083785621642599</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="S3">
+            <v>17.143345555100598</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="S4">
+            <v>9.6810900661572106</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="S5">
+            <v>12.4094630110907</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="S6">
+            <v>12.047781394951199</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="S7">
+            <v>9.3230113493137399</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="S8">
+            <v>7.5010861563244404</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="S9">
+            <v>10.5604950347146</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="S10">
+            <v>17.3824601151248</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="S11">
+            <v>15.0876473125918</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="S12">
+            <v>18.4355457317779</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="S13">
+            <v>23.6632212970819</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="S14">
+            <v>32.943420041709203</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="S15">
+            <v>22.794639633259902</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="S16">
+            <v>18.196679699128801</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="S17">
+            <v>18.1464971044898</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="S18">
+            <v>19.760804665560901</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="S19">
+            <v>23.6038108825623</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="S20">
+            <v>22.852053700559001</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="S21">
+            <v>27.5886923837915</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="S22">
+            <v>36.355978565502397</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="S23">
+            <v>41.941696866512501</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="S24">
+            <v>37.836353167124003</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="S25">
+            <v>39.179539171813197</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="S26">
+            <v>28.637649902619899</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="S27">
+            <v>31.187111837703998</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="S28">
+            <v>33.904752112670799</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="S29">
+            <v>51.474823212449998</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="S30">
+            <v>34.348114150707303</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="S31">
+            <v>42.583800030746403</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="S32">
+            <v>46.397465323985998</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="S33">
+            <v>48.373571549456102</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="S34">
+            <v>50.860022967645698</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="S35">
+            <v>37.174171698462402</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="S36">
+            <v>49.922518770279403</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="S37">
+            <v>45.999429511537798</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="S38">
+            <v>53.152202672213498</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="S39">
+            <v>43.234620308464798</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="S40">
+            <v>41.4585412081234</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="S41">
+            <v>41.528653421660202</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="S42">
+            <v>46.195567330139703</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="S43">
+            <v>58.533857538790997</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="S44">
+            <v>60.2272524101462</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="S45">
+            <v>67.511100291182004</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="S46">
+            <v>68.170568689243694</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="S47">
+            <v>59.613596140198602</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="S48">
+            <v>66.975869128180193</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="S49">
+            <v>75.606264778819394</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="S50">
+            <v>58.8164965154836</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="S51">
+            <v>73.981243168061198</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -913,10 +1702,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A300D066-D769-B241-98BC-0CA3EEA4CA40}">
-  <dimension ref="A1:R51"/>
+  <dimension ref="A1:S51"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B1" t="s">
         <v>1</v>
       </c>
@@ -968,8 +1757,11 @@
       <c r="R1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -1024,8 +1816,12 @@
       <c r="R2">
         <v>1.7748832702636701E-2</v>
       </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S2" s="1">
+        <f>(N2-'[1]MM-roma5'!S2)/'[1]MM-roma5'!S2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -1080,8 +1876,12 @@
       <c r="R3">
         <v>2.03058719635009E-2</v>
       </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S3" s="1">
+        <f>(N3-'[1]MM-roma5'!S3)/'[1]MM-roma5'!S3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -1136,8 +1936,12 @@
       <c r="R4">
         <v>1.47271156311035E-2</v>
       </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S4" s="1">
+        <f>(N4-'[1]MM-roma5'!S4)/'[1]MM-roma5'!S4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -1192,8 +1996,12 @@
       <c r="R5">
         <v>1.4057159423828101E-2</v>
       </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S5" s="1">
+        <f>(N5-'[1]MM-roma5'!S5)/'[1]MM-roma5'!S5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -1248,8 +2056,12 @@
       <c r="R6">
         <v>2.1093130111694301E-2</v>
       </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S6" s="1">
+        <f>(N6-'[1]MM-roma5'!S6)/'[1]MM-roma5'!S6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -1304,8 +2116,12 @@
       <c r="R7">
         <v>1.34909152984619E-2</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="1">
+        <f>(N7-'[1]MM-roma5'!S7)/'[1]MM-roma5'!S7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -1360,8 +2176,12 @@
       <c r="R8">
         <v>1.8097162246704102E-2</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="1">
+        <f>(N8-'[1]MM-roma5'!S8)/'[1]MM-roma5'!S8</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -1416,8 +2236,12 @@
       <c r="R9">
         <v>1.3319969177246E-2</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="1">
+        <f>(N9-'[1]MM-roma5'!S9)/'[1]MM-roma5'!S9</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -1472,8 +2296,12 @@
       <c r="R10">
         <v>1.2444019317626899E-2</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="1">
+        <f>(N10-'[1]MM-roma5'!S10)/'[1]MM-roma5'!S10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -1528,8 +2356,12 @@
       <c r="R11">
         <v>1.35040283203125E-2</v>
       </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="1">
+        <f>(N11-'[1]MM-roma5'!S11)/'[1]MM-roma5'!S11</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -1584,8 +2416,12 @@
       <c r="R12">
         <v>4.8609972000122001E-2</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="1">
+        <f>(N12-'[1]MM-roma5'!S12)/'[1]MM-roma5'!S12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>29</v>
       </c>
@@ -1640,8 +2476,12 @@
       <c r="R13">
         <v>8.0765962600707994E-2</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="1">
+        <f>(N13-'[1]MM-roma5'!S13)/'[1]MM-roma5'!S13</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>30</v>
       </c>
@@ -1696,8 +2536,12 @@
       <c r="R14">
         <v>0.46974396705627403</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="1">
+        <f>(N14-'[1]MM-roma5'!S14)/'[1]MM-roma5'!S14</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -1752,8 +2596,12 @@
       <c r="R15">
         <v>6.87382221221923E-2</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="1">
+        <f>(N15-'[1]MM-roma5'!S15)/'[1]MM-roma5'!S15</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>32</v>
       </c>
@@ -1808,8 +2656,12 @@
       <c r="R16">
         <v>6.8354129791259696E-2</v>
       </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="1">
+        <f>(N16-'[1]MM-roma5'!S16)/'[1]MM-roma5'!S16</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>33</v>
       </c>
@@ -1864,8 +2716,12 @@
       <c r="R17">
         <v>7.0106029510498005E-2</v>
       </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="1">
+        <f>(N17-'[1]MM-roma5'!S17)/'[1]MM-roma5'!S17</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -1920,8 +2776,12 @@
       <c r="R18">
         <v>6.0922145843505797E-2</v>
       </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="1">
+        <f>(N18-'[1]MM-roma5'!S18)/'[1]MM-roma5'!S18</f>
+        <v>1.3484629122094912E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>35</v>
       </c>
@@ -1976,8 +2836,12 @@
       <c r="R19">
         <v>6.9540977478027302E-2</v>
       </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="1">
+        <f>(N19-'[1]MM-roma5'!S19)/'[1]MM-roma5'!S19</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>36</v>
       </c>
@@ -2032,8 +2896,12 @@
       <c r="R20">
         <v>6.5388917922973605E-2</v>
       </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="1">
+        <f>(N20-'[1]MM-roma5'!S20)/'[1]MM-roma5'!S20</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>37</v>
       </c>
@@ -2088,8 +2956,12 @@
       <c r="R21">
         <v>8.6126089096069294E-2</v>
       </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="1">
+        <f>(N21-'[1]MM-roma5'!S21)/'[1]MM-roma5'!S21</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>38</v>
       </c>
@@ -2144,8 +3016,12 @@
       <c r="R22">
         <v>0.19485521316528301</v>
       </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="1">
+        <f>(N22-'[1]MM-roma5'!S22)/'[1]MM-roma5'!S22</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>39</v>
       </c>
@@ -2200,8 +3076,12 @@
       <c r="R23">
         <v>0.18482708930969199</v>
       </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="1">
+        <f>(N23-'[1]MM-roma5'!S23)/'[1]MM-roma5'!S23</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>40</v>
       </c>
@@ -2256,8 +3136,12 @@
       <c r="R24">
         <v>0.241061925888061</v>
       </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="1">
+        <f>(N24-'[1]MM-roma5'!S24)/'[1]MM-roma5'!S24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>41</v>
       </c>
@@ -2312,8 +3196,12 @@
       <c r="R25">
         <v>0.18508386611938399</v>
       </c>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="1">
+        <f>(N25-'[1]MM-roma5'!S25)/'[1]MM-roma5'!S25</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>42</v>
       </c>
@@ -2368,8 +3256,12 @@
       <c r="R26">
         <v>0.184641122817993</v>
       </c>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="1">
+        <f>(N26-'[1]MM-roma5'!S26)/'[1]MM-roma5'!S26</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>43</v>
       </c>
@@ -2424,8 +3316,12 @@
       <c r="R27">
         <v>0.14945411682128901</v>
       </c>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="1">
+        <f>(N27-'[1]MM-roma5'!S27)/'[1]MM-roma5'!S27</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>44</v>
       </c>
@@ -2480,8 +3376,12 @@
       <c r="R28">
         <v>0.18969225883483801</v>
       </c>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="1">
+        <f>(N28-'[1]MM-roma5'!S28)/'[1]MM-roma5'!S28</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>45</v>
       </c>
@@ -2536,8 +3436,12 @@
       <c r="R29">
         <v>0.17643380165100001</v>
       </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="1">
+        <f>(N29-'[1]MM-roma5'!S29)/'[1]MM-roma5'!S29</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>46</v>
       </c>
@@ -2592,8 +3496,12 @@
       <c r="R30">
         <v>0.187011003494262</v>
       </c>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="1">
+        <f>(N30-'[1]MM-roma5'!S30)/'[1]MM-roma5'!S30</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>47</v>
       </c>
@@ -2648,8 +3556,12 @@
       <c r="R31">
         <v>0.17992973327636699</v>
       </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="1">
+        <f>(N31-'[1]MM-roma5'!S31)/'[1]MM-roma5'!S31</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>48</v>
       </c>
@@ -2704,8 +3616,12 @@
       <c r="R32">
         <v>0.434206962585449</v>
       </c>
-    </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="1">
+        <f>(N32-'[1]MM-roma5'!S32)/'[1]MM-roma5'!S32</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>49</v>
       </c>
@@ -2760,8 +3676,12 @@
       <c r="R33">
         <v>0.41746997833251898</v>
       </c>
-    </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="1">
+        <f>(N33-'[1]MM-roma5'!S33)/'[1]MM-roma5'!S33</f>
+        <v>2.0588221422259259E-15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>50</v>
       </c>
@@ -2816,8 +3736,12 @@
       <c r="R34">
         <v>0.418294668197631</v>
       </c>
-    </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="1">
+        <f>(N34-'[1]MM-roma5'!S34)/'[1]MM-roma5'!S34</f>
+        <v>2.1833731573931954E-3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>51</v>
       </c>
@@ -2872,8 +3796,12 @@
       <c r="R35">
         <v>0.40453243255615201</v>
       </c>
-    </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="1">
+        <f>(N35-'[1]MM-roma5'!S35)/'[1]MM-roma5'!S35</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>52</v>
       </c>
@@ -2928,8 +3856,12 @@
       <c r="R36">
         <v>0.37429618835449202</v>
       </c>
-    </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S36" s="1">
+        <f>(N36-'[1]MM-roma5'!S36)/'[1]MM-roma5'!S36</f>
+        <v>-2.6044118698570767E-15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>53</v>
       </c>
@@ -2984,8 +3916,12 @@
       <c r="R37">
         <v>0.48008513450622498</v>
       </c>
-    </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S37" s="1">
+        <f>(N37-'[1]MM-roma5'!S37)/'[1]MM-roma5'!S37</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>54</v>
       </c>
@@ -3040,8 +3976,12 @@
       <c r="R38">
         <v>0.35352611541748002</v>
       </c>
-    </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="1">
+        <f>(N38-'[1]MM-roma5'!S38)/'[1]MM-roma5'!S38</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>55</v>
       </c>
@@ -3096,8 +4036,12 @@
       <c r="R39">
         <v>0.31539392471313399</v>
       </c>
-    </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="1">
+        <f>(N39-'[1]MM-roma5'!S39)/'[1]MM-roma5'!S39</f>
+        <v>-2.7751689196672489E-15</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>56</v>
       </c>
@@ -3152,8 +4096,12 @@
       <c r="R40">
         <v>0.43746161460876398</v>
       </c>
-    </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="1">
+        <f>(N40-'[1]MM-roma5'!S40)/'[1]MM-roma5'!S40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>57</v>
       </c>
@@ -3208,8 +4156,12 @@
       <c r="R41">
         <v>0.40770888328552202</v>
       </c>
-    </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="1">
+        <f>(N41-'[1]MM-roma5'!S41)/'[1]MM-roma5'!S41</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>58</v>
       </c>
@@ -3264,8 +4216,12 @@
       <c r="R42">
         <v>0.76744008064269997</v>
       </c>
-    </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="1">
+        <f>(N42-'[1]MM-roma5'!S42)/'[1]MM-roma5'!S42</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>59</v>
       </c>
@@ -3320,8 +4276,12 @@
       <c r="R43">
         <v>0.756664037704467</v>
       </c>
-    </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="1">
+        <f>(N43-'[1]MM-roma5'!S43)/'[1]MM-roma5'!S43</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>60</v>
       </c>
@@ -3376,8 +4336,12 @@
       <c r="R44">
         <v>0.84271097183227495</v>
       </c>
-    </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="1">
+        <f>(N44-'[1]MM-roma5'!S44)/'[1]MM-roma5'!S44</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>61</v>
       </c>
@@ -3432,8 +4396,12 @@
       <c r="R45">
         <v>0.68738508224487305</v>
       </c>
-    </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="1">
+        <f>(N45-'[1]MM-roma5'!S45)/'[1]MM-roma5'!S45</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>62</v>
       </c>
@@ -3488,8 +4456,12 @@
       <c r="R46">
         <v>0.89690589904785101</v>
       </c>
-    </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="1">
+        <f>(N46-'[1]MM-roma5'!S46)/'[1]MM-roma5'!S46</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>63</v>
       </c>
@@ -3544,8 +4516,12 @@
       <c r="R47">
         <v>0.73049187660217196</v>
       </c>
-    </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="1">
+        <f>(N47-'[1]MM-roma5'!S47)/'[1]MM-roma5'!S47</f>
+        <v>1.5781378802067419E-15</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>64</v>
       </c>
@@ -3600,8 +4576,12 @@
       <c r="R48">
         <v>0.82997226715087802</v>
       </c>
-    </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="1">
+        <f>(N48-'[1]MM-roma5'!S48)/'[1]MM-roma5'!S48</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>65</v>
       </c>
@@ -3656,8 +4636,12 @@
       <c r="R49">
         <v>0.62148880958557096</v>
       </c>
-    </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="1">
+        <f>(N49-'[1]MM-roma5'!S49)/'[1]MM-roma5'!S49</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>66</v>
       </c>
@@ -3712,8 +4696,12 @@
       <c r="R50">
         <v>0.70627784729003895</v>
       </c>
-    </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="1">
+        <f>(N50-'[1]MM-roma5'!S50)/'[1]MM-roma5'!S50</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>67</v>
       </c>
@@ -3767,6 +4755,10 @@
       </c>
       <c r="R51">
         <v>0.79108309745788497</v>
+      </c>
+      <c r="S51" s="1">
+        <f>(N51-'[1]MM-roma5'!S51)/'[1]MM-roma5'!S51</f>
+        <v>1.5057029745256935E-15</v>
       </c>
     </row>
   </sheetData>
@@ -3776,10 +4768,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A165B350-9024-9C41-822F-1CDCE8547BC4}">
-  <dimension ref="A1:R51"/>
+  <dimension ref="A1:S51"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B1" t="s">
         <v>1</v>
       </c>
@@ -3831,8 +4823,11 @@
       <c r="R1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>68</v>
       </c>
@@ -3887,8 +4882,12 @@
       <c r="R2">
         <v>2.70981788635253E-2</v>
       </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S2" s="1">
+        <f>(N2-'[1]MM-napoli5'!S2)/'[1]MM-napoli5'!S2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>69</v>
       </c>
@@ -3943,8 +4942,12 @@
       <c r="R3">
         <v>1.12230777740478E-2</v>
       </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S3" s="1">
+        <f>(N3-'[1]MM-napoli5'!S3)/'[1]MM-napoli5'!S3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>70</v>
       </c>
@@ -3999,8 +5002,12 @@
       <c r="R4">
         <v>1.00140571594238E-2</v>
       </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S4" s="1">
+        <f>(N4-'[1]MM-napoli5'!S4)/'[1]MM-napoli5'!S4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>71</v>
       </c>
@@ -4055,8 +5062,12 @@
       <c r="R5">
         <v>1.1503219604492101E-2</v>
       </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S5" s="1">
+        <f>(N5-'[1]MM-napoli5'!S5)/'[1]MM-napoli5'!S5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>72</v>
       </c>
@@ -4111,8 +5122,12 @@
       <c r="R6">
         <v>1.2332916259765601E-2</v>
       </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S6" s="1">
+        <f>(N6-'[1]MM-napoli5'!S6)/'[1]MM-napoli5'!S6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>73</v>
       </c>
@@ -4167,8 +5182,12 @@
       <c r="R7">
         <v>1.4176130294799799E-2</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="1">
+        <f>(N7-'[1]MM-napoli5'!S7)/'[1]MM-napoli5'!S7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>74</v>
       </c>
@@ -4223,8 +5242,12 @@
       <c r="R8">
         <v>1.4529943466186499E-2</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="1">
+        <f>(N8-'[1]MM-napoli5'!S8)/'[1]MM-napoli5'!S8</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>75</v>
       </c>
@@ -4279,8 +5302,12 @@
       <c r="R9">
         <v>1.23357772827148E-2</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="1">
+        <f>(N9-'[1]MM-napoli5'!S9)/'[1]MM-napoli5'!S9</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>76</v>
       </c>
@@ -4335,8 +5362,12 @@
       <c r="R10">
         <v>1.09391212463378E-2</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="1">
+        <f>(N10-'[1]MM-napoli5'!S10)/'[1]MM-napoli5'!S10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>77</v>
       </c>
@@ -4391,8 +5422,12 @@
       <c r="R11">
         <v>8.7990760803222604E-3</v>
       </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="1">
+        <f>(N11-'[1]MM-napoli5'!S11)/'[1]MM-napoli5'!S11</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>78</v>
       </c>
@@ -4447,8 +5482,12 @@
       <c r="R12">
         <v>4.2185068130493102E-2</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="1">
+        <f>(N12-'[1]MM-napoli5'!S12)/'[1]MM-napoli5'!S12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>79</v>
       </c>
@@ -4503,8 +5542,12 @@
       <c r="R13">
         <v>5.6545972824096603E-2</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="1">
+        <f>(N13-'[1]MM-napoli5'!S13)/'[1]MM-napoli5'!S13</f>
+        <v>1.8274002624623868E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>80</v>
       </c>
@@ -4559,8 +5602,12 @@
       <c r="R14">
         <v>4.9409866333007799E-2</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="1">
+        <f>(N14-'[1]MM-napoli5'!S14)/'[1]MM-napoli5'!S14</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>81</v>
       </c>
@@ -4615,8 +5662,12 @@
       <c r="R15">
         <v>6.1674118041992097E-2</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="1">
+        <f>(N15-'[1]MM-napoli5'!S15)/'[1]MM-napoli5'!S15</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>82</v>
       </c>
@@ -4671,8 +5722,12 @@
       <c r="R16">
         <v>5.25760650634765E-2</v>
       </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="1">
+        <f>(N16-'[1]MM-napoli5'!S16)/'[1]MM-napoli5'!S16</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>83</v>
       </c>
@@ -4727,8 +5782,12 @@
       <c r="R17">
         <v>6.5798759460449205E-2</v>
       </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="1">
+        <f>(N17-'[1]MM-napoli5'!S17)/'[1]MM-napoli5'!S17</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>84</v>
       </c>
@@ -4783,8 +5842,12 @@
       <c r="R18">
         <v>6.3558816909789997E-2</v>
       </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="1">
+        <f>(N18-'[1]MM-napoli5'!S18)/'[1]MM-napoli5'!S18</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>85</v>
       </c>
@@ -4839,8 +5902,12 @@
       <c r="R19">
         <v>5.8573722839355399E-2</v>
       </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="1">
+        <f>(N19-'[1]MM-napoli5'!S19)/'[1]MM-napoli5'!S19</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>86</v>
       </c>
@@ -4895,8 +5962,12 @@
       <c r="R20">
         <v>4.37359809875488E-2</v>
       </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="1">
+        <f>(N20-'[1]MM-napoli5'!S20)/'[1]MM-napoli5'!S20</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>87</v>
       </c>
@@ -4951,8 +6022,12 @@
       <c r="R21">
         <v>6.41300678253173E-2</v>
       </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="1">
+        <f>(N21-'[1]MM-napoli5'!S21)/'[1]MM-napoli5'!S21</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>88</v>
       </c>
@@ -5007,8 +6082,12 @@
       <c r="R22">
         <v>0.123486995697021</v>
       </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="1">
+        <f>(N22-'[1]MM-napoli5'!S22)/'[1]MM-napoli5'!S22</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>89</v>
       </c>
@@ -5063,8 +6142,12 @@
       <c r="R23">
         <v>0.13069415092468201</v>
       </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="1">
+        <f>(N23-'[1]MM-napoli5'!S23)/'[1]MM-napoli5'!S23</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>90</v>
       </c>
@@ -5119,8 +6202,12 @@
       <c r="R24">
         <v>0.12883877754211401</v>
       </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="1">
+        <f>(N24-'[1]MM-napoli5'!S24)/'[1]MM-napoli5'!S24</f>
+        <v>1.580500742083905E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>91</v>
       </c>
@@ -5175,8 +6262,12 @@
       <c r="R25">
         <v>0.134056091308593</v>
       </c>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="1">
+        <f>(N25-'[1]MM-napoli5'!S25)/'[1]MM-napoli5'!S25</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>92</v>
       </c>
@@ -5231,8 +6322,12 @@
       <c r="R26">
         <v>0.15803623199462799</v>
       </c>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="1">
+        <f>(N26-'[1]MM-napoli5'!S26)/'[1]MM-napoli5'!S26</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>93</v>
       </c>
@@ -5287,8 +6382,12 @@
       <c r="R27">
         <v>9.7254753112792899E-2</v>
       </c>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="1">
+        <f>(N27-'[1]MM-napoli5'!S27)/'[1]MM-napoli5'!S27</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>94</v>
       </c>
@@ -5343,8 +6442,12 @@
       <c r="R28">
         <v>0.14543390274047799</v>
       </c>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="1">
+        <f>(N28-'[1]MM-napoli5'!S28)/'[1]MM-napoli5'!S28</f>
+        <v>3.4292699930525701E-15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>95</v>
       </c>
@@ -5399,8 +6502,12 @@
       <c r="R29">
         <v>0.169346094131469</v>
       </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="1">
+        <f>(N29-'[1]MM-napoli5'!S29)/'[1]MM-napoli5'!S29</f>
+        <v>-2.5398563014190697E-15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>96</v>
       </c>
@@ -5455,8 +6562,12 @@
       <c r="R30">
         <v>0.17125177383422799</v>
       </c>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="1">
+        <f>(N30-'[1]MM-napoli5'!S30)/'[1]MM-napoli5'!S30</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>97</v>
       </c>
@@ -5511,8 +6622,12 @@
       <c r="R31">
         <v>0.15824103355407701</v>
       </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="1">
+        <f>(N31-'[1]MM-napoli5'!S31)/'[1]MM-napoli5'!S31</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>98</v>
       </c>
@@ -5567,8 +6682,12 @@
       <c r="R32">
         <v>0.320041894912719</v>
       </c>
-    </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="1">
+        <f>(N32-'[1]MM-napoli5'!S32)/'[1]MM-napoli5'!S32</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>99</v>
       </c>
@@ -5623,8 +6742,12 @@
       <c r="R33">
         <v>0.34972810745239202</v>
       </c>
-    </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="1">
+        <f>(N33-'[1]MM-napoli5'!S33)/'[1]MM-napoli5'!S33</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>100</v>
       </c>
@@ -5679,8 +6802,12 @@
       <c r="R34">
         <v>0.31208777427673301</v>
       </c>
-    </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="1">
+        <f>(N34-'[1]MM-napoli5'!S34)/'[1]MM-napoli5'!S34</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>101</v>
       </c>
@@ -5735,8 +6862,12 @@
       <c r="R35">
         <v>0.32000994682312001</v>
       </c>
-    </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="1">
+        <f>(N35-'[1]MM-napoli5'!S35)/'[1]MM-napoli5'!S35</f>
+        <v>-2.346516400053241E-15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>102</v>
       </c>
@@ -5791,8 +6922,12 @@
       <c r="R36">
         <v>0.33355093002319303</v>
       </c>
-    </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S36" s="1">
+        <f>(N36-'[1]MM-napoli5'!S36)/'[1]MM-napoli5'!S36</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>103</v>
       </c>
@@ -5847,8 +6982,12 @@
       <c r="R37">
         <v>0.30745697021484297</v>
       </c>
-    </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S37" s="1">
+        <f>(N37-'[1]MM-napoli5'!S37)/'[1]MM-napoli5'!S37</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>104</v>
       </c>
@@ -5903,8 +7042,12 @@
       <c r="R38">
         <v>0.32052087783813399</v>
       </c>
-    </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="1">
+        <f>(N38-'[1]MM-napoli5'!S38)/'[1]MM-napoli5'!S38</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>105</v>
       </c>
@@ -5959,8 +7102,12 @@
       <c r="R39">
         <v>0.32158827781677202</v>
       </c>
-    </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="1">
+        <f>(N39-'[1]MM-napoli5'!S39)/'[1]MM-napoli5'!S39</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>106</v>
       </c>
@@ -6015,8 +7162,12 @@
       <c r="R40">
         <v>0.28808712959289501</v>
       </c>
-    </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="1">
+        <f>(N40-'[1]MM-napoli5'!S40)/'[1]MM-napoli5'!S40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>107</v>
       </c>
@@ -6071,8 +7222,12 @@
       <c r="R41">
         <v>0.29760098457336398</v>
       </c>
-    </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="1">
+        <f>(N41-'[1]MM-napoli5'!S41)/'[1]MM-napoli5'!S41</f>
+        <v>5.980298810912007E-3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>108</v>
       </c>
@@ -6127,8 +7282,12 @@
       <c r="R42">
         <v>0.56074905395507801</v>
       </c>
-    </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="1">
+        <f>(N42-'[1]MM-napoli5'!S42)/'[1]MM-napoli5'!S42</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>109</v>
       </c>
@@ -6183,8 +7342,12 @@
       <c r="R43">
         <v>0.53175091743469205</v>
       </c>
-    </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="1">
+        <f>(N43-'[1]MM-napoli5'!S43)/'[1]MM-napoli5'!S43</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>110</v>
       </c>
@@ -6239,8 +7402,12 @@
       <c r="R44">
         <v>0.71158695220947199</v>
       </c>
-    </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="1">
+        <f>(N44-'[1]MM-napoli5'!S44)/'[1]MM-napoli5'!S44</f>
+        <v>-1.1556833090105243E-5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>111</v>
       </c>
@@ -6295,8 +7462,12 @@
       <c r="R45">
         <v>0.49493908882141102</v>
       </c>
-    </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="1">
+        <f>(N45-'[1]MM-napoli5'!S45)/'[1]MM-napoli5'!S45</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>112</v>
       </c>
@@ -6351,8 +7522,12 @@
       <c r="R46">
         <v>0.59485912322998002</v>
       </c>
-    </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="1">
+        <f>(N46-'[1]MM-napoli5'!S46)/'[1]MM-napoli5'!S46</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>113</v>
       </c>
@@ -6407,8 +7582,12 @@
       <c r="R47">
         <v>0.48348522186279203</v>
       </c>
-    </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="1">
+        <f>(N47-'[1]MM-napoli5'!S47)/'[1]MM-napoli5'!S47</f>
+        <v>3.2104931818027101E-3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>114</v>
       </c>
@@ -6463,8 +7642,12 @@
       <c r="R48">
         <v>0.51548790931701605</v>
       </c>
-    </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="1">
+        <f>(N48-'[1]MM-napoli5'!S48)/'[1]MM-napoli5'!S48</f>
+        <v>-1.2584629620291411E-6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>115</v>
       </c>
@@ -6519,8 +7702,12 @@
       <c r="R49">
         <v>0.51317596435546797</v>
       </c>
-    </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="1">
+        <f>(N49-'[1]MM-napoli5'!S49)/'[1]MM-napoli5'!S49</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>116</v>
       </c>
@@ -6575,8 +7762,12 @@
       <c r="R50">
         <v>0.54674291610717696</v>
       </c>
-    </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="1">
+        <f>(N50-'[1]MM-napoli5'!S50)/'[1]MM-napoli5'!S50</f>
+        <v>2.0146723248323805E-15</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>117</v>
       </c>
@@ -6630,6 +7821,10 @@
       </c>
       <c r="R51">
         <v>0.51191616058349598</v>
+      </c>
+      <c r="S51" s="1">
+        <f>(N51-'[1]MM-napoli5'!S51)/'[1]MM-napoli5'!S51</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6639,10 +7834,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B477FC84-9766-DF4A-A0B3-BE37B62EF7DF}">
-  <dimension ref="A1:R51"/>
+  <dimension ref="A1:S51"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B1" t="s">
         <v>1</v>
       </c>
@@ -6694,8 +7889,11 @@
       <c r="R1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>118</v>
       </c>
@@ -6750,8 +7948,12 @@
       <c r="R2">
         <v>2.0766973495483398E-2</v>
       </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S2" s="1">
+        <f>(N2-'[1]MM-milano5'!S2)/'[1]MM-milano5'!S2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>119</v>
       </c>
@@ -6806,8 +8008,12 @@
       <c r="R3">
         <v>1.56807899475097E-2</v>
       </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S3" s="1">
+        <f>(N3-'[1]MM-milano5'!S3)/'[1]MM-milano5'!S3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>120</v>
       </c>
@@ -6862,8 +8068,12 @@
       <c r="R4">
         <v>1.4793872833251899E-2</v>
       </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S4" s="1">
+        <f>(N4-'[1]MM-milano5'!S4)/'[1]MM-milano5'!S4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>121</v>
       </c>
@@ -6918,8 +8128,12 @@
       <c r="R5">
         <v>1.6015291213989199E-2</v>
       </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S5" s="1">
+        <f>(N5-'[1]MM-milano5'!S5)/'[1]MM-milano5'!S5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>122</v>
       </c>
@@ -6974,8 +8188,12 @@
       <c r="R6">
         <v>1.7930984497070299E-2</v>
       </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S6" s="1">
+        <f>(N6-'[1]MM-milano5'!S6)/'[1]MM-milano5'!S6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>123</v>
       </c>
@@ -7030,8 +8248,12 @@
       <c r="R7">
         <v>1.29132270812988E-2</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="1">
+        <f>(N7-'[1]MM-milano5'!S7)/'[1]MM-milano5'!S7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>124</v>
       </c>
@@ -7086,8 +8308,12 @@
       <c r="R8">
         <v>1.33259296417236E-2</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="1">
+        <f>(N8-'[1]MM-milano5'!S8)/'[1]MM-milano5'!S8</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>125</v>
       </c>
@@ -7142,8 +8368,12 @@
       <c r="R9">
         <v>1.71351432800292E-2</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="1">
+        <f>(N9-'[1]MM-milano5'!S9)/'[1]MM-milano5'!S9</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>126</v>
       </c>
@@ -7198,8 +8428,12 @@
       <c r="R10">
         <v>1.92492008209228E-2</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="1">
+        <f>(N10-'[1]MM-milano5'!S10)/'[1]MM-milano5'!S10</f>
+        <v>8.944526122773435E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>127</v>
       </c>
@@ -7254,8 +8488,12 @@
       <c r="R11">
         <v>1.6504049301147398E-2</v>
       </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="1">
+        <f>(N11-'[1]MM-milano5'!S11)/'[1]MM-milano5'!S11</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>128</v>
       </c>
@@ -7310,8 +8548,12 @@
       <c r="R12">
         <v>6.4071893692016602E-2</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="1">
+        <f>(N12-'[1]MM-milano5'!S12)/'[1]MM-milano5'!S12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>129</v>
       </c>
@@ -7366,8 +8608,12 @@
       <c r="R13">
         <v>5.8759927749633699E-2</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="1">
+        <f>(N13-'[1]MM-milano5'!S13)/'[1]MM-milano5'!S13</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>130</v>
       </c>
@@ -7422,8 +8668,12 @@
       <c r="R14">
         <v>8.3214282989501898E-2</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="1">
+        <f>(N14-'[1]MM-milano5'!S14)/'[1]MM-milano5'!S14</f>
+        <v>3.019600966762676E-15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>131</v>
       </c>
@@ -7478,8 +8728,12 @@
       <c r="R15">
         <v>5.4666280746459898E-2</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="1">
+        <f>(N15-'[1]MM-milano5'!S15)/'[1]MM-milano5'!S15</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>132</v>
       </c>
@@ -7534,8 +8788,12 @@
       <c r="R16">
         <v>5.20071983337402E-2</v>
       </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="1">
+        <f>(N16-'[1]MM-milano5'!S16)/'[1]MM-milano5'!S16</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>133</v>
       </c>
@@ -7590,8 +8848,12 @@
       <c r="R17">
         <v>6.0647964477539E-2</v>
       </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="1">
+        <f>(N17-'[1]MM-milano5'!S17)/'[1]MM-milano5'!S17</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>134</v>
       </c>
@@ -7646,8 +8908,12 @@
       <c r="R18">
         <v>5.7102203369140597E-2</v>
       </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="1">
+        <f>(N18-'[1]MM-milano5'!S18)/'[1]MM-milano5'!S18</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>135</v>
       </c>
@@ -7702,8 +8968,12 @@
       <c r="R19">
         <v>6.4359903335571206E-2</v>
       </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="1">
+        <f>(N19-'[1]MM-milano5'!S19)/'[1]MM-milano5'!S19</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>136</v>
       </c>
@@ -7758,8 +9028,12 @@
       <c r="R20">
         <v>5.3756952285766602E-2</v>
       </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="1">
+        <f>(N20-'[1]MM-milano5'!S20)/'[1]MM-milano5'!S20</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>137</v>
       </c>
@@ -7814,8 +9088,12 @@
       <c r="R21">
         <v>6.8139076232910101E-2</v>
       </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="1">
+        <f>(N21-'[1]MM-milano5'!S21)/'[1]MM-milano5'!S21</f>
+        <v>-3.6056795161794866E-15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>138</v>
       </c>
@@ -7870,8 +9148,12 @@
       <c r="R22">
         <v>0.156725883483886</v>
       </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="1">
+        <f>(N22-'[1]MM-milano5'!S22)/'[1]MM-milano5'!S22</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>139</v>
       </c>
@@ -7926,8 +9208,12 @@
       <c r="R23">
         <v>0.21896600723266599</v>
       </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="1">
+        <f>(N23-'[1]MM-milano5'!S23)/'[1]MM-milano5'!S23</f>
+        <v>2.3717682029655461E-15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>140</v>
       </c>
@@ -7982,8 +9268,12 @@
       <c r="R24">
         <v>0.196835041046142</v>
       </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="1">
+        <f>(N24-'[1]MM-milano5'!S24)/'[1]MM-milano5'!S24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>141</v>
       </c>
@@ -8038,8 +9328,12 @@
       <c r="R25">
         <v>0.16611313819885201</v>
       </c>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="1">
+        <f>(N25-'[1]MM-milano5'!S25)/'[1]MM-milano5'!S25</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>142</v>
       </c>
@@ -8094,8 +9388,12 @@
       <c r="R26">
         <v>0.14439201354980399</v>
       </c>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="1">
+        <f>(N26-'[1]MM-milano5'!S26)/'[1]MM-milano5'!S26</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>143</v>
       </c>
@@ -8150,8 +9448,12 @@
       <c r="R27">
         <v>0.13869595527648901</v>
       </c>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="1">
+        <f>(N27-'[1]MM-milano5'!S27)/'[1]MM-milano5'!S27</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>144</v>
       </c>
@@ -8206,8 +9508,12 @@
       <c r="R28">
         <v>0.197045803070068</v>
       </c>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="1">
+        <f>(N28-'[1]MM-milano5'!S28)/'[1]MM-milano5'!S28</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>145</v>
       </c>
@@ -8262,8 +9568,12 @@
       <c r="R29">
         <v>0.338088989257812</v>
       </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="1">
+        <f>(N29-'[1]MM-milano5'!S29)/'[1]MM-milano5'!S29</f>
+        <v>4.0301831165343123E-3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>146</v>
       </c>
@@ -8318,8 +9628,12 @@
       <c r="R30">
         <v>0.20206832885742099</v>
       </c>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="1">
+        <f>(N30-'[1]MM-milano5'!S30)/'[1]MM-milano5'!S30</f>
+        <v>1.3503195178004938E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>147</v>
       </c>
@@ -8374,8 +9688,12 @@
       <c r="R31">
         <v>0.20009875297546301</v>
       </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="1">
+        <f>(N31-'[1]MM-milano5'!S31)/'[1]MM-milano5'!S31</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>148</v>
       </c>
@@ -8430,8 +9748,12 @@
       <c r="R32">
         <v>0.35670208930969199</v>
       </c>
-    </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="1">
+        <f>(N32-'[1]MM-milano5'!S32)/'[1]MM-milano5'!S32</f>
+        <v>-2.1439960634010784E-15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>149</v>
       </c>
@@ -8486,8 +9808,12 @@
       <c r="R33">
         <v>0.38806390762329102</v>
       </c>
-    </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="1">
+        <f>(N33-'[1]MM-milano5'!S33)/'[1]MM-milano5'!S33</f>
+        <v>-2.0564117930534012E-15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>150</v>
       </c>
@@ -8542,8 +9868,12 @@
       <c r="R34">
         <v>0.38473415374755798</v>
       </c>
-    </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="1">
+        <f>(N34-'[1]MM-milano5'!S34)/'[1]MM-milano5'!S34</f>
+        <v>4.2148780157702462E-3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>151</v>
       </c>
@@ -8598,8 +9928,12 @@
       <c r="R35">
         <v>0.34734916687011702</v>
       </c>
-    </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="1">
+        <f>(N35-'[1]MM-milano5'!S35)/'[1]MM-milano5'!S35</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>152</v>
       </c>
@@ -8654,8 +9988,12 @@
       <c r="R36">
         <v>0.39379596710205</v>
       </c>
-    </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S36" s="1">
+        <f>(N36-'[1]MM-milano5'!S36)/'[1]MM-milano5'!S36</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>153</v>
       </c>
@@ -8710,8 +10048,12 @@
       <c r="R37">
         <v>0.37276697158813399</v>
       </c>
-    </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S37" s="1">
+        <f>(N37-'[1]MM-milano5'!S37)/'[1]MM-milano5'!S37</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>154</v>
       </c>
@@ -8766,8 +10108,12 @@
       <c r="R38">
         <v>0.36001157760620101</v>
       </c>
-    </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="1">
+        <f>(N38-'[1]MM-milano5'!S38)/'[1]MM-milano5'!S38</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>155</v>
       </c>
@@ -8822,8 +10168,12 @@
       <c r="R39">
         <v>0.28859615325927701</v>
       </c>
-    </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="1">
+        <f>(N39-'[1]MM-milano5'!S39)/'[1]MM-milano5'!S39</f>
+        <v>4.6084127523838263E-3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>156</v>
       </c>
@@ -8878,8 +10228,12 @@
       <c r="R40">
         <v>0.359560966491699</v>
       </c>
-    </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="1">
+        <f>(N40-'[1]MM-milano5'!S40)/'[1]MM-milano5'!S40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>157</v>
       </c>
@@ -8934,8 +10288,12 @@
       <c r="R41">
         <v>0.36515212059020902</v>
       </c>
-    </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="1">
+        <f>(N41-'[1]MM-milano5'!S41)/'[1]MM-milano5'!S41</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>158</v>
       </c>
@@ -8990,8 +10348,12 @@
       <c r="R42">
         <v>0.81633925437927202</v>
       </c>
-    </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="1">
+        <f>(N42-'[1]MM-milano5'!S42)/'[1]MM-milano5'!S42</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>159</v>
       </c>
@@ -9046,8 +10408,12 @@
       <c r="R43">
         <v>0.72664380073547297</v>
       </c>
-    </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="1">
+        <f>(N43-'[1]MM-milano5'!S43)/'[1]MM-milano5'!S43</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>160</v>
       </c>
@@ -9102,8 +10468,12 @@
       <c r="R44">
         <v>0.61599206924438399</v>
       </c>
-    </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="1">
+        <f>(N44-'[1]MM-milano5'!S44)/'[1]MM-milano5'!S44</f>
+        <v>1.5660915825625486E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>161</v>
       </c>
@@ -9158,8 +10528,12 @@
       <c r="R45">
         <v>0.79066801071166903</v>
       </c>
-    </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="1">
+        <f>(N45-'[1]MM-milano5'!S45)/'[1]MM-milano5'!S45</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>162</v>
       </c>
@@ -9214,8 +10588,12 @@
       <c r="R46">
         <v>0.69442892074584905</v>
       </c>
-    </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="1">
+        <f>(N46-'[1]MM-milano5'!S46)/'[1]MM-milano5'!S46</f>
+        <v>-1.4592218448385903E-15</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>163</v>
       </c>
@@ -9270,8 +10648,12 @@
       <c r="R47">
         <v>0.70581459999084395</v>
       </c>
-    </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="1">
+        <f>(N47-'[1]MM-milano5'!S47)/'[1]MM-milano5'!S47</f>
+        <v>1.6686794531312538E-15</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>164</v>
       </c>
@@ -9326,8 +10708,12 @@
       <c r="R48">
         <v>0.66292905807495095</v>
       </c>
-    </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="1">
+        <f>(N48-'[1]MM-milano5'!S48)/'[1]MM-milano5'!S48</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>165</v>
       </c>
@@ -9382,8 +10768,12 @@
       <c r="R49">
         <v>0.71674895286560003</v>
       </c>
-    </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="1">
+        <f>(N49-'[1]MM-milano5'!S49)/'[1]MM-milano5'!S49</f>
+        <v>-1.3157108514409983E-15</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>166</v>
       </c>
@@ -9438,8 +10828,12 @@
       <c r="R50">
         <v>0.5707368850708</v>
       </c>
-    </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="1">
+        <f>(N50-'[1]MM-milano5'!S50)/'[1]MM-milano5'!S50</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>167</v>
       </c>
@@ -9493,6 +10887,10 @@
       </c>
       <c r="R51">
         <v>0.811961889266967</v>
+      </c>
+      <c r="S51" s="1">
+        <f>(N51-'[1]MM-milano5'!S51)/'[1]MM-milano5'!S51</f>
+        <v>1.3446108600856721E-15</v>
       </c>
     </row>
   </sheetData>
